--- a/AAII_Financials/Quarterly/LEGN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEGN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -656,297 +656,304 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE7" s="2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>387500</v>
+      </c>
+      <c r="E8" s="3">
         <v>305100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>306400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>272300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>255100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>94000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>79500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>96000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>73300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>117000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>50000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>40100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>57300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10100</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="3">
         <v>10100</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>261600</v>
+        <v>137400</v>
       </c>
       <c r="E9" s="3">
-        <v>224800</v>
+        <v>175900</v>
       </c>
       <c r="F9" s="3">
-        <v>228500</v>
+        <v>123500</v>
       </c>
       <c r="G9" s="3">
-        <v>196300</v>
+        <v>115300</v>
       </c>
       <c r="H9" s="3">
-        <v>173200</v>
+        <v>98000</v>
       </c>
       <c r="I9" s="3">
-        <v>178300</v>
+        <v>71300</v>
       </c>
       <c r="J9" s="3">
+        <v>73900</v>
+      </c>
+      <c r="K9" s="3">
         <v>151000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>163100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>155700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>138100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>139300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>128500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -992,59 +999,62 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>43500</v>
+        <v>250100</v>
       </c>
       <c r="E10" s="3">
-        <v>81600</v>
+        <v>129200</v>
       </c>
       <c r="F10" s="3">
-        <v>43900</v>
+        <v>182900</v>
       </c>
       <c r="G10" s="3">
-        <v>58800</v>
+        <v>157000</v>
       </c>
       <c r="H10" s="3">
-        <v>21800</v>
+        <v>157100</v>
       </c>
       <c r="I10" s="3">
-        <v>8300</v>
+        <v>123700</v>
       </c>
       <c r="J10" s="3">
+        <v>112600</v>
+      </c>
+      <c r="K10" s="3">
         <v>9200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-61700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-58700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-43300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-55100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-84200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>51600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-4900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1100,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,106 +1139,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E12" s="3">
         <v>85700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>113100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>98300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>101900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>104400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>95500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>112600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>101000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>105700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>95900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>95800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>84900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>335600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>68800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>81500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>86500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>72300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>154500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>71100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>66900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>63700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>53600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>48000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>161900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>21300</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE12" s="3">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="3">
         <v>21300</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,53 +1339,56 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>4400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1420,53 +1440,56 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2400</v>
       </c>
       <c r="H15" s="3">
         <v>2300</v>
       </c>
       <c r="I15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>329800</v>
+      </c>
+      <c r="E17" s="3">
         <v>354900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>327000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>315800</v>
       </c>
-      <c r="G17" s="3">
-        <v>276900</v>
-      </c>
       <c r="H17" s="3">
+        <v>277000</v>
+      </c>
+      <c r="I17" s="3">
         <v>246700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>261500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>230600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>228500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>211900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>200500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>188500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>160700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>554200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>197200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>115500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>156500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>103700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>202700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>93200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>100300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>79000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>147600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>58000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>194200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>25200</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF17" s="3">
         <v>25200</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-49800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-43500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-21900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-51700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-74900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-70400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-42000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-117900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-121100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-92500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-104300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-124300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-437200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-185200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-65500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-138500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-86800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-168800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-79500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-60200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-67300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-136000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-46500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-136900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-15100</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-15100</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,151 +1816,155 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>6400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
-        <v>108900</v>
-      </c>
       <c r="H20" s="3">
+        <v>108800</v>
+      </c>
+      <c r="I20" s="3">
         <v>55000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-112500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>62100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-49200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>37100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-30000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>89300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>33400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-38000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2600</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF20" s="3">
         <v>2600</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-53800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-42300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-128300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-128400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-104400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-131300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-65000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-155400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-59800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-191500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-111200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1955,85 +1992,88 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-45900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-124900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E22" s="3">
         <v>4200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>4500</v>
       </c>
       <c r="G22" s="3">
         <v>4500</v>
       </c>
       <c r="H22" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I22" s="3">
         <v>4600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5800</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>5200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2047,8 +2087,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -2056,12 +2096,12 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2077,163 +2117,169 @@
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-53100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-124800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-99200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>40500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-120900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-59800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-146800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-62500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-198800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-112000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-445700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-193100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-32100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-109300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-124800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-173100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-80900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-58400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-67100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-47900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-130400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>600</v>
       </c>
       <c r="G24" s="3">
         <v>600</v>
       </c>
       <c r="H24" s="3">
+        <v>600</v>
+      </c>
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>-3600</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2241,31 +2287,31 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-37700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-500</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
@@ -2273,8 +2319,11 @@
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-125400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-101000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>26300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-125300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-59800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-144800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-62200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-199100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-112100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-446300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-193200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-32300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-105700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-124800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-173100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-80900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-66500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-134900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-125400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-101000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>26300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-125300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-59800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-144800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-62200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-199100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-112100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-446300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-193200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-32300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-105700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-124800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-173100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-80900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-66500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-108900</v>
-      </c>
       <c r="H32" s="3">
+        <v>-108800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-55000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>112500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-62100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>49200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-37100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>30000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-89300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-33400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>38000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-125400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-101000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>26300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-125300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-59800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-144800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-62200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-199100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-112100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-446300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-193200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-32300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-105700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-124800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-173100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-80900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-66500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-125400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-101000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>26300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-125300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-59800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-144800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-62200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-199100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-112100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-446300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-193200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-32300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-105700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-124800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-173100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-80900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-66500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE38" s="2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,86 +3612,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>672900</v>
+      </c>
+      <c r="E41" s="3">
         <v>646400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>901900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>278900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>266600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>441700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>286700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>459300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>201300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>897600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1277700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>963500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1233200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>660100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>786000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>379800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>786000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>688900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>338300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>488200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>412300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>455700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>449400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>562400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>168800</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,86 +3711,89 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>291700</v>
+      </c>
+      <c r="E42" s="3">
         <v>188200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>46700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>713700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>701000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>563700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>835900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>753100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1090600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>404800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>460400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>281600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>190100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>240900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>404700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>270900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>194900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>298100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>204700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>50300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>50400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>127200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>75800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>77900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,85 +3812,88 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E43" s="3">
         <v>186600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>250300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>202600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>229000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>166800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>125100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>104000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>78000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>157100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>62900</v>
-      </c>
-      <c r="P43" s="3">
-        <v>100</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
       </c>
       <c r="R43" s="3">
+        <v>100</v>
+      </c>
+      <c r="S43" s="3">
         <v>1100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>50500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15000</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>75600</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
+      <c r="AB43" s="3">
+        <v>0</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
@@ -3808,8 +3901,8 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -3820,86 +3913,89 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E44" s="3">
         <v>37100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>29200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1300</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3918,19 +4014,22 @@
       <c r="AH44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E45" s="3">
         <v>5000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -3938,14 +4037,14 @@
       <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
@@ -3957,47 +4056,47 @@
         <v>400</v>
       </c>
       <c r="O45" s="3">
+        <v>400</v>
+      </c>
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>61800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>61800</v>
-      </c>
-      <c r="T45" s="3">
-        <v>13800</v>
       </c>
       <c r="U45" s="3">
         <v>13800</v>
       </c>
       <c r="V45" s="3">
+        <v>13800</v>
+      </c>
+      <c r="W45" s="3">
         <v>11200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>33500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>23200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4016,86 +4115,89 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1227400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1082700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1247100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1242000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1249900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1218800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1283900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1350000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1424800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1413800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1497800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1508800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1612900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>915400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1099100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>835900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1099100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>949900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>653400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>720800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>475100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>593900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>602700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>673400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>271200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4114,8 +4216,11 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4137,11 +4242,11 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>4500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4400</v>
       </c>
       <c r="L47" s="3">
         <v>4400</v>
@@ -4150,50 +4255,50 @@
         <v>4400</v>
       </c>
       <c r="N47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O47" s="3">
         <v>4300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1900</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4212,86 +4317,89 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>448200</v>
+      </c>
+      <c r="E48" s="3">
         <v>452500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>401500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>253700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>233600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>206000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>201200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>203500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>219700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>185500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>189200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>184300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>189500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>190500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>160800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>145600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>160800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>140800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>148600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>142500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>130500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>111900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>104200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>96400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>91300</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4310,8 +4418,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4325,71 +4436,71 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>2100</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>2500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1000</v>
       </c>
       <c r="Z49" s="3">
         <v>1000</v>
       </c>
       <c r="AA49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4408,8 +4519,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,77 +4721,80 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E52" s="3">
         <v>61500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>85100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>217200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>204300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>188700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>185100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>175300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>146400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>168300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>153200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>137900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>121600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>96800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>66800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>22000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4690,8 +4810,8 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -4702,8 +4822,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,86 +4923,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1750900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1596700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1733700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1712900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1689900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1615600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1670200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1735800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1798200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1775100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1848600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1839300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1930700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1209400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1331000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1022700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1331000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1119500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>813800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>875100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>615300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>722100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>708600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>772900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>364900</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4898,8 +5024,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,86 +5100,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E57" s="3">
         <v>74300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>83000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>102500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>75400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>58100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>38600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26900</v>
-      </c>
-      <c r="K57" s="3">
-        <v>39500</v>
       </c>
       <c r="L57" s="3">
         <v>39500</v>
       </c>
       <c r="M57" s="3">
+        <v>39500</v>
+      </c>
+      <c r="N57" s="3">
         <v>30700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>29800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>217000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>129100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>217000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>130600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>99000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>120200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>89700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>105000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>75300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>67400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>64900</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5068,86 +5199,89 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>168200</v>
+      </c>
+      <c r="E58" s="3">
         <v>277200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>326500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>150200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1200</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1500</v>
       </c>
       <c r="X58" s="3">
         <v>1500</v>
       </c>
       <c r="Y58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1400</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,86 +5300,89 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E59" s="3">
         <v>157600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>103900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>180900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>184200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>113100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>169800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>98400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>119000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>96600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>121000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>203800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>142800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>97700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>175200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>139700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>54700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>64100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>46800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>46100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5264,86 +5401,89 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>403600</v>
+      </c>
+      <c r="E60" s="3">
         <v>509100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>636400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>433600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>265500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>234400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>277700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>270900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>294300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>249700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>216400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>175200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>201400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>238200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>297800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>259800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>297800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>229200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>275400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>261100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>145900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>115600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>123500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>115000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>112400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5362,86 +5502,89 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E61" s="3">
         <v>112100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>87200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>260000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>382000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>357500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>345800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>342200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>335600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>331600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>325500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>317600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>315100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>310200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>281000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>193600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>281000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>122100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>72400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>153800</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5460,86 +5603,89 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E62" s="3">
         <v>7800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
       <c r="O62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>200</v>
       </c>
       <c r="Q62" s="3">
+        <v>200</v>
+      </c>
+      <c r="R62" s="3">
         <v>7900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>253700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>240100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>255200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>261200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>281900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>247700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>254700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>265000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5558,8 +5704,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,86 +6007,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>521300</v>
+      </c>
+      <c r="E66" s="3">
         <v>629000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>731600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>701700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>654400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>597900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>629600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>619700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>639200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>611000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>597200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>499700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>523600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>556200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>586700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>460100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>586700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>353500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>587900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>535200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>408800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>124300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>373700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>371900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>531300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5950,8 +6108,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,86 +6549,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1979600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2012800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1958500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1927700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1888000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1762700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1661700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1688000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1562700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1544500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1484700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1339900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1277700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>744300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>562600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>744300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>765900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>225800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>339900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>206400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>597700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>334900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>401000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-166400</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6476,8 +6650,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,86 +6953,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1229600</v>
+      </c>
+      <c r="E76" s="3">
         <v>967700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1002100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1011300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1035500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1017700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1040600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1116100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1159000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1164100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1251400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1339600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1407000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>653200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>744300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>562600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>744300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>765900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>225900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>339900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>206500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>597800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>334900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>401000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-166300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6868,8 +7054,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE80" s="2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-125400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-101000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>26300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-125300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-59800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-144800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-62200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-199100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-112100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-446300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-193200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-32300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-105700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-124800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-173100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-80900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-66500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,61 +7401,62 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3">
         <v>5100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4400</v>
       </c>
       <c r="M83" s="3">
         <v>4400</v>
       </c>
       <c r="N83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O83" s="3">
         <v>4300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3400</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7274,35 +7473,38 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>600</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3">
         <v>600</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-85100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28800</v>
       </c>
-      <c r="G89" s="3">
-        <v>-13000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-103600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-82000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-75800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-95600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-60800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-97600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-139200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-201300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>119800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-69500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-44600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3">
         <v>196200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-55900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-64400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-56900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-45800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-83100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8145,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7934,44 +8155,44 @@
         <v>-7500</v>
       </c>
       <c r="E91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -7996,35 +8217,38 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8446,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-168000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>638500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-165500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>256600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-87900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>329100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-695600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-396100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>407500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-209100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-121700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>16000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-77100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-37500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>96500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-105700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3">
         <v>7000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>61200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-58600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-58700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-114900</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-114900</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8397,8 +8631,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,195 +8988,201 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>167700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>790000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>378000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>-626600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>323600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>-618700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>459800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>148800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>14700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>28700</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF100" s="3">
         <v>28700</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-800</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>3</v>
@@ -8941,102 +9190,108 @@
       <c r="AH101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-255500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>623100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-175100</v>
-      </c>
       <c r="H102" s="3">
+        <v>-175200</v>
+      </c>
+      <c r="I102" s="3">
         <v>155000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-172600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>258000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-696300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-380100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>314200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-269700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>573200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>97100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-544400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>350600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-149900</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
         <v>-415700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-113000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>393600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>85400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-126800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
